--- a/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0002T0006Z000C1N14_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0002T0006Z000C1N14_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>2.643677116575033</v>
+        <v>0.4295975314434429</v>
       </c>
       <c r="D2" t="n">
-        <v>2.274036394139662</v>
+        <v>0.3695309140476951</v>
       </c>
       <c r="E2" t="n">
-        <v>11.27302051196897</v>
+        <v>1.831865833194958</v>
       </c>
       <c r="F2" t="n">
-        <v>11.47775877456908</v>
+        <v>1.865135800867475</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>33.71320821432445</v>
+        <v>5.478396334827724</v>
       </c>
       <c r="D3" t="n">
-        <v>33.83114229517867</v>
+        <v>5.497560622966534</v>
       </c>
       <c r="E3" t="n">
-        <v>11.27302051196897</v>
+        <v>1.831865833194958</v>
       </c>
       <c r="F3" t="n">
-        <v>11.47775877456908</v>
+        <v>1.865135800867475</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>35.43119668928603</v>
+        <v>5.75756946200898</v>
       </c>
       <c r="D4" t="n">
-        <v>34.721650799206</v>
+        <v>5.642268254870975</v>
       </c>
       <c r="E4" t="n">
-        <v>11.27302051196897</v>
+        <v>1.831865833194958</v>
       </c>
       <c r="F4" t="n">
-        <v>11.47775877456908</v>
+        <v>1.865135800867475</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>16.93417817223772</v>
+        <v>2.75180395298863</v>
       </c>
       <c r="D5" t="n">
-        <v>16.39283714595192</v>
+        <v>2.663836036217187</v>
       </c>
       <c r="E5" t="n">
-        <v>11.27302051196897</v>
+        <v>1.831865833194958</v>
       </c>
       <c r="F5" t="n">
-        <v>11.47775877456908</v>
+        <v>1.865135800867475</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>18.7863658786399</v>
+        <v>3.052784455278984</v>
       </c>
       <c r="D6" t="n">
-        <v>17.925678514768</v>
+        <v>2.9129227586498</v>
       </c>
       <c r="E6" t="n">
-        <v>11.27302051196897</v>
+        <v>1.831865833194958</v>
       </c>
       <c r="F6" t="n">
-        <v>11.47775877456908</v>
+        <v>1.865135800867475</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>31.88581288156081</v>
+        <v>5.181444593253632</v>
       </c>
       <c r="D7" t="n">
-        <v>31.41589877447461</v>
+        <v>5.105083550852124</v>
       </c>
       <c r="E7" t="n">
-        <v>11.27302051196897</v>
+        <v>1.831865833194958</v>
       </c>
       <c r="F7" t="n">
-        <v>11.47775877456908</v>
+        <v>1.865135800867475</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>29.85335386520516</v>
+        <v>4.851170003095839</v>
       </c>
       <c r="D8" t="n">
-        <v>29.76538307715255</v>
+        <v>4.83687475003729</v>
       </c>
       <c r="E8" t="n">
-        <v>11.27302051196897</v>
+        <v>1.831865833194958</v>
       </c>
       <c r="F8" t="n">
-        <v>11.47775877456908</v>
+        <v>1.865135800867475</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>37.79352253219136</v>
+        <v>6.141447411481097</v>
       </c>
       <c r="D9" t="n">
-        <v>38.40676300892825</v>
+        <v>6.241098988950841</v>
       </c>
       <c r="E9" t="n">
-        <v>11.27302051196897</v>
+        <v>1.831865833194958</v>
       </c>
       <c r="F9" t="n">
-        <v>11.47775877456908</v>
+        <v>1.865135800867475</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
